--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmayores_a_2018_o_higgins.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:51</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>-0.36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.07</v>
@@ -566,13 +566,13 @@
         <v>-0.7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>-0.51</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.2</v>
@@ -589,16 +589,16 @@
         <v>-0.37</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.26</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="5">
@@ -612,13 +612,13 @@
         <v>0.45</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.2</v>
@@ -632,19 +632,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.41</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="7">
@@ -655,19 +655,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="8">
@@ -678,16 +678,16 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.16</v>
@@ -704,13 +704,13 @@
         <v>0.1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.16</v>
@@ -724,19 +724,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="11">
@@ -747,19 +747,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="12">
@@ -770,16 +770,16 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.05</v>
@@ -796,16 +796,16 @@
         <v>0.2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>0.23</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.03</v>
@@ -839,19 +839,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>0.03</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>338</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -865,13 +865,13 @@
         <v>-0.3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>-0.04</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.26</v>
@@ -888,13 +888,13 @@
         <v>-0.46</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.21</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.25</v>
@@ -911,13 +911,13 @@
         <v>-0.87</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.66</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.21</v>
